--- a/event_planner_forms/010_halloween_costume_quiz--event_planner_forms.xlsx
+++ b/event_planner_forms/010_halloween_costume_quiz--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>the_shawshank_redemption</t>
+          <t>the shawshank redemption</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>the_goonies</t>
+          <t>the goonies</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>the_matrix</t>
+          <t>the matrix</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>harry_potter</t>
+          <t>harry potter</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>the_hobbit</t>
+          <t>the hobbit</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>the_illusionist</t>
+          <t>the illusionist</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>led_zepplin</t>
+          <t>led zepplin</t>
         </is>
       </c>
     </row>
@@ -1964,29 +1964,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>fortnite</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>fortnite</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>favorite_game_choices</t>
+          <t>favorite_music_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>fortnite</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>fortnite</t>
+          <t>rock</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>electronic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>electronic</t>
         </is>
       </c>
     </row>
@@ -2015,29 +2015,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>electronic</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>electronic</t>
+          <t>classical</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>favorite_music_choices</t>
+          <t>favorite_halloween_costume_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>classical</t>
+          <t>ghost</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>classical</t>
+          <t>ghost</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ghost</t>
+          <t>vampire</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ghost</t>
+          <t>vampire</t>
         </is>
       </c>
     </row>
@@ -2066,27 +2066,10 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>vampire</t>
+          <t>mummy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
-        <is>
-          <t>vampire</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>favorite_halloween_costume_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>mummy</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
         <is>
           <t>mummy</t>
         </is>
